--- a/artfynd/A 31336-2021 artfynd.xlsx
+++ b/artfynd/A 31336-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31336-2021 artfynd.xlsx
+++ b/artfynd/A 31336-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>91286537</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523239.2553697182</v>
+        <v>523239</v>
       </c>
       <c r="R2" t="n">
-        <v>6965327.737263739</v>
+        <v>6965328</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
